--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -136,6 +136,15 @@
     <t>攻击增幅</t>
   </si>
   <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
     <t>特殊奖励，只有此等级奖励一次，不会增加</t>
   </si>
   <si>
@@ -149,6 +158,12 @@
   </si>
   <si>
     <t>爆伤</t>
+  </si>
+  <si>
+    <t>致命</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1437,6 +1452,75 @@
         <v>22</v>
       </c>
     </row>
+    <row r="16" customHeight="1" spans="3:9">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>800</v>
+      </c>
+      <c r="E16" s="1">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>900</v>
+      </c>
+      <c r="E17" s="1">
+        <v>50</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>10002</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>50</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A28" s="1" t="s">
         <v>0</v>
@@ -1447,7 +1531,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1470,7 +1554,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:9">
@@ -1493,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -1516,7 +1600,7 @@
         <v>5</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -1539,7 +1623,53 @@
         <v>25</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:9">
+      <c r="C33" s="1">
+        <v>105</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>23</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:9">
+      <c r="C34" s="1">
+        <v>106</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>24</v>
+      </c>
+      <c r="H34" s="1">
+        <v>25</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>#</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>致命伤害</t>
+  </si>
+  <si>
+    <t>宠物备战位+1</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1672,6 +1675,29 @@
         <v>32</v>
       </c>
     </row>
+    <row r="35" customHeight="1" spans="3:9">
+      <c r="C35" s="1">
+        <v>107</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2100</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2</v>
+      </c>
+      <c r="G35" s="1">
+        <v>111</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3:I5 C3:G5" errorStyle="warning">

--- a/Excel/BabelAtrConfig.xlsx
+++ b/Excel/BabelAtrConfig.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>致命伤害</t>
-  </si>
-  <si>
-    <t>宠物备战位+1</t>
   </si>
 </sst>
 </file>
@@ -1689,13 +1686,13 @@
         <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>111</v>
+        <v>10001</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
